--- a/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699427</t>
+    <t>10699547</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Shana</t>
-  </si>
-  <si>
-    <t>Altenwerth</t>
+    <t>Augustus</t>
+  </si>
+  <si>
+    <t>Beahan</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 58681602</t>
+    <t>Auto 69342354</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699407</t>
+    <t>10699548</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Electa</t>
-  </si>
-  <si>
-    <t>Sporer</t>
+    <t>Johanna</t>
+  </si>
+  <si>
+    <t>Graham</t>
   </si>
   <si>
     <t>No</t>
@@ -399,7 +399,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,6 +409,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,7 +530,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -532,8 +541,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -560,7 +569,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -580,7 +589,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -590,8 +599,8 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -600,14 +609,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -619,7 +628,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1097,7 +1106,7 @@
       <c r="AR1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="7" t="s">
         <v>41</v>
       </c>
       <c r="AT1" s="3" t="s">
@@ -1141,158 +1150,158 @@
       <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45774</v>
-      </c>
-      <c r="M2" s="9" t="s">
+        <v>45779</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="17">
         <v>21201</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="U2" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="20">
         <f>L2</f>
-        <v>45774</v>
-      </c>
-      <c r="Y2" s="14">
+        <v>45779</v>
+      </c>
+      <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45825</v>
-      </c>
-      <c r="Z2" s="20" t="s">
+        <v>45830</v>
+      </c>
+      <c r="Z2" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AB2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="AD2" s="22" t="s">
+      <c r="AD2" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="AE2" s="24">
+      <c r="AE2" s="25">
         <v>124</v>
       </c>
-      <c r="AF2" s="24" t="s">
+      <c r="AF2" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AG2" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="AH2" s="25">
+      <c r="AH2" s="26">
         <v>40</v>
       </c>
-      <c r="AI2" s="22" t="s">
+      <c r="AI2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AJ2" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="19" t="s">
+      <c r="AK2" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AL2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="13" t="s">
+      <c r="AM2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AN2" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AO2" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AP2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AQ2" s="9" t="s">
+      <c r="AQ2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR2" s="27" t="s">
+      <c r="AR2" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="AS2" s="28">
+      <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>266854395</v>
-      </c>
-      <c r="AT2" s="22" t="s">
+        <v>854488220</v>
+      </c>
+      <c r="AT2" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="AU2" s="29">
+      <c r="AU2" s="30">
         <v>35591</v>
       </c>
-      <c r="AV2" s="9" t="s">
+      <c r="AV2" s="10" t="s">
         <v>57</v>
       </c>
       <c r="AW2" t="s">
         <v>84</v>
       </c>
-      <c r="AX2" s="9" t="s">
+      <c r="AX2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AY2" s="9" t="s">
+      <c r="AY2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AZ2" s="30">
+      <c r="AZ2" s="31">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
@@ -1315,157 +1324,157 @@
       <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="35">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45774</v>
-      </c>
-      <c r="M3" s="26" t="s">
+        <v>45779</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="17">
         <v>21201</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="35" t="s">
+      <c r="S3" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="T3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="U3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="36" t="s">
+      <c r="V3" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45774</v>
-      </c>
-      <c r="Y3" s="34">
+        <v>45779</v>
+      </c>
+      <c r="Y3" s="35">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45825</v>
-      </c>
-      <c r="Z3" s="37" t="s">
+        <v>45830</v>
+      </c>
+      <c r="Z3" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="AA3" s="38" t="s">
+      <c r="AA3" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="AB3" s="39" t="s">
+      <c r="AB3" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AC3" s="40" t="s">
+      <c r="AC3" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="AD3" s="39" t="s">
+      <c r="AD3" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="41">
+      <c r="AE3" s="42">
         <v>121</v>
       </c>
-      <c r="AF3" s="42" t="s">
+      <c r="AF3" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="AG3" s="24" t="s">
+      <c r="AG3" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="AH3" s="43">
+      <c r="AH3" s="44">
         <v>10</v>
       </c>
-      <c r="AI3" s="39" t="s">
+      <c r="AI3" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="AJ3" s="39" t="s">
+      <c r="AJ3" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="AK3" s="44" t="s">
+      <c r="AK3" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="AL3" s="26" t="s">
+      <c r="AL3" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="AM3" s="26" t="s">
+      <c r="AM3" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="AN3" s="39" t="s">
+      <c r="AN3" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="AO3" s="26" t="s">
+      <c r="AO3" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AP3" s="26" t="s">
+      <c r="AP3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="AQ3" s="26" t="s">
+      <c r="AQ3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AR3" s="26" t="s">
+      <c r="AR3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AS3" s="45">
-        <v>827727883</v>
-      </c>
-      <c r="AT3" s="39" t="s">
+      <c r="AS3" s="46">
+        <v>311108850</v>
+      </c>
+      <c r="AT3" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="AU3" s="46">
+      <c r="AU3" s="47">
         <v>35226</v>
       </c>
-      <c r="AV3" s="26" t="s">
+      <c r="AV3" s="27" t="s">
         <v>57</v>
       </c>
       <c r="AW3" t="s">
         <v>84</v>
       </c>
-      <c r="AX3" s="26" t="s">
+      <c r="AX3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AY3" s="26" t="s">
+      <c r="AY3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="AZ3" s="30">
+      <c r="AZ3" s="31">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">

--- a/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F8A95-E556-478B-BD07-50CA0F1DBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -178,12 +192,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699547</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
   </si>
   <si>
@@ -281,9 +289,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699548</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
@@ -322,81 +327,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF040C28"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="14"/>
       <color theme="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF4A4A4A"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -408,7 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,7 +430,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,8 +462,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -468,15 +477,25 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -487,7 +506,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -502,9 +523,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -913,9 +940,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -973,7 +1000,7 @@
     <col min="57" max="57" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1143,99 +1170,94 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="G2" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="L2" s="15">
+        <f ca="1">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="P2" s="16" t="s">
         <v>63</v>
-      </c>
-      <c r="L2" s="15">
-        <f>TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="P2" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="Q2" s="17">
         <v>21201</v>
       </c>
       <c r="R2" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" s="18" t="s">
+      <c r="W2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="X2" s="20">
+        <f ca="1">L2</f>
+        <v>45786</v>
+      </c>
+      <c r="Y2" s="15">
+        <f ca="1">TODAY()+20</f>
+        <v>45837</v>
+      </c>
+      <c r="Z2" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="AA2" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="X2" s="20">
-        <f>L2</f>
-        <v>45779</v>
-      </c>
-      <c r="Y2" s="15">
-        <f>TODAY()+20</f>
-        <v>45830</v>
-      </c>
-      <c r="Z2" s="21" t="s">
+      <c r="AB2" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" s="22" t="s">
+      <c r="AC2" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" s="23" t="s">
+      <c r="AD2" s="23" t="s">
         <v>71</v>
-      </c>
-      <c r="AC2" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="23" t="s">
-        <v>73</v>
       </c>
       <c r="AE2" s="25">
         <v>124</v>
@@ -1244,284 +1266,262 @@
         <v>47</v>
       </c>
       <c r="AG2" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH2" s="26">
         <v>40</v>
       </c>
       <c r="AI2" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="23" t="s">
+      <c r="AM2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AN2" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="14" t="s">
+      <c r="AO2" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="23" t="s">
+      <c r="AP2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="27" t="s">
+      <c r="AQ2" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AR2" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="10" t="s">
+      <c r="AS2" s="29">
+        <f t="array" aca="1" ref="AS2:AS3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>225001536</v>
+      </c>
+      <c r="AT2" s="23" t="s">
         <v>81</v>
-      </c>
-      <c r="AQ2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="AR2" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS2" s="29">
-        <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>854488220</v>
-      </c>
-      <c r="AT2" s="23" t="s">
-        <v>83</v>
       </c>
       <c r="AU2" s="30">
         <v>35591</v>
       </c>
       <c r="AV2" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AW2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AX2" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AY2" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ2" s="31">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD2" t="s">
         <v>85</v>
       </c>
-      <c r="BC2" t="s">
+    </row>
+    <row r="3" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>86</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H3" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="I3" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="35">
+        <f t="shared" ref="L3" ca="1" si="0">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="27" t="s">
+      <c r="N3" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="P3" s="36" t="s">
         <v>63</v>
-      </c>
-      <c r="L3" s="35">
-        <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="O3" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" s="36" t="s">
-        <v>65</v>
       </c>
       <c r="Q3" s="17">
         <v>21201</v>
       </c>
       <c r="R3" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="U3" s="27" t="s">
+      <c r="W3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="X3" s="20">
+        <f t="shared" ref="X3" ca="1" si="1">L3</f>
+        <v>45786</v>
+      </c>
+      <c r="Y3" s="35">
+        <f t="shared" ref="Y3" ca="1" si="2">TODAY()+20</f>
+        <v>45837</v>
+      </c>
+      <c r="Z3" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="X3" s="20">
-        <f t="shared" ref="X3" si="1">L3</f>
-        <v>45779</v>
-      </c>
-      <c r="Y3" s="35">
-        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45830</v>
-      </c>
-      <c r="Z3" s="38" t="s">
-        <v>69</v>
-      </c>
       <c r="AA3" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" s="40" t="s">
         <v>93</v>
-      </c>
-      <c r="AB3" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC3" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD3" s="40" t="s">
-        <v>96</v>
       </c>
       <c r="AE3" s="42">
         <v>121</v>
       </c>
       <c r="AF3" s="43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AG3" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH3" s="44">
         <v>10</v>
       </c>
       <c r="AI3" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ3" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK3" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL3" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="AJ3" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK3" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL3" s="27" t="s">
-        <v>77</v>
-      </c>
       <c r="AM3" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AO3" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AP3" s="27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AQ3" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AR3" s="27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AS3" s="46">
-        <v>311108850</v>
+        <f ca="1"/>
+        <v>988557136</v>
       </c>
       <c r="AT3" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AU3" s="47">
         <v>35226</v>
       </c>
       <c r="AV3" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AW3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AX3" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AY3" s="27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ3" s="31">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BB3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD3" t="s">
         <v>85</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 Z3 W3 T3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/27/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F8A95-E556-478B-BD07-50CA0F1DBA8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -192,6 +178,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699753</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
   </si>
   <si>
@@ -201,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Augustus</t>
-  </si>
-  <si>
-    <t>Beahan</t>
+    <t>Rylan</t>
+  </si>
+  <si>
+    <t>Heller</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -234,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 69342354</t>
+    <t>Auto 66682893</t>
   </si>
   <si>
     <t>Regular</t>
@@ -291,13 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699754</t>
+  </si>
+  <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Johanna</t>
-  </si>
-  <si>
-    <t>Graham</t>
+    <t>Korbin</t>
+  </si>
+  <si>
+    <t>Stroman</t>
   </si>
   <si>
     <t>No</t>
@@ -327,81 +322,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF040C28"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF040C28"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color theme="10"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF4A4A4A"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF4A4A4A"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -413,7 +408,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,7 +425,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,12 +457,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -477,25 +468,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -506,9 +487,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -523,15 +502,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -940,9 +913,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -1000,7 +973,7 @@
     <col min="57" max="57" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,94 +1143,99 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="15">
+        <f>TODAY()-31</f>
+        <v>45795</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="15">
-        <f ca="1">TODAY()-31</f>
-        <v>45786</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N2" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="17">
         <v>21201</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U2" s="18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V2" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="X2" s="20">
-        <f ca="1">L2</f>
-        <v>45786</v>
+        <f>L2</f>
+        <v>45795</v>
       </c>
       <c r="Y2" s="15">
-        <f ca="1">TODAY()+20</f>
-        <v>45837</v>
+        <f>TODAY()+20</f>
+        <v>45846</v>
       </c>
       <c r="Z2" s="21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA2" s="22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB2" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC2" s="24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AE2" s="25">
         <v>124</v>
@@ -1266,262 +1244,284 @@
         <v>47</v>
       </c>
       <c r="AG2" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AH2" s="26">
         <v>40</v>
       </c>
       <c r="AI2" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK2" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="AK2" s="20" t="s">
-        <v>72</v>
-      </c>
       <c r="AL2" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AM2" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AN2" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AO2" s="27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AP2" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AQ2" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AR2" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS2" s="29">
-        <f t="array" aca="1" ref="AS2:AS3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>225001536</v>
+        <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>352276525</v>
       </c>
       <c r="AT2" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AU2" s="30">
         <v>35591</v>
       </c>
       <c r="AV2" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AW2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AX2" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AY2" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AZ2" s="31">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="BB2" t="s">
-        <v>83</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>84</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>61</v>
-      </c>
       <c r="L3" s="35">
-        <f t="shared" ref="L3" ca="1" si="0">TODAY()-31</f>
-        <v>45786</v>
+        <f t="shared" ref="L3" si="0">TODAY()-31</f>
+        <v>45795</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N3" s="36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O3" s="36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P3" s="36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="17">
         <v>21201</v>
       </c>
       <c r="R3" s="36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S3" s="36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T3" s="27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W3" s="27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="X3" s="20">
-        <f t="shared" ref="X3" ca="1" si="1">L3</f>
-        <v>45786</v>
+        <f t="shared" ref="X3" si="1">L3</f>
+        <v>45795</v>
       </c>
       <c r="Y3" s="35">
-        <f t="shared" ref="Y3" ca="1" si="2">TODAY()+20</f>
-        <v>45837</v>
+        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
+        <v>45846</v>
       </c>
       <c r="Z3" s="38" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="39" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="40" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AC3" s="41" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AD3" s="40" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AE3" s="42">
         <v>121</v>
       </c>
       <c r="AF3" s="43" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AG3" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AH3" s="44">
         <v>10</v>
       </c>
       <c r="AI3" s="40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AJ3" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK3" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="AK3" s="45" t="s">
-        <v>72</v>
-      </c>
       <c r="AL3" s="27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AM3" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO3" s="27" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AP3" s="27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AQ3" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AR3" s="27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS3" s="46">
-        <f ca="1"/>
-        <v>988557136</v>
+        <v>649131264</v>
       </c>
       <c r="AT3" s="40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AU3" s="47">
         <v>35226</v>
       </c>
       <c r="AV3" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AW3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AX3" s="27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AY3" s="27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AZ3" s="31">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="BB3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="BC3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BD3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 Z3 W3 T3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>